--- a/data/trans_orig/P36BPD02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023</t>
+          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023 (tasa de respuesta: 96,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51337</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>86503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>50897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110949</t>
+          <t>111123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212365</t>
+          <t>215254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260338</t>
+          <t>260155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198570</t>
+          <t>198959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235292</t>
+          <t>237004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423373</t>
+          <t>423976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485118</t>
+          <t>482336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>166843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209936</t>
+          <t>208673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141557</t>
+          <t>143243</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175445</t>
+          <t>177865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>318046</t>
+          <t>320674</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>374276</t>
+          <t>377294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69090</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>53475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77164</t>
+          <t>79148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113403</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184485</t>
+          <t>186297</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228194</t>
+          <t>228371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154210</t>
+          <t>153454</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186815</t>
+          <t>186422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>347885</t>
+          <t>347872</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>401707</t>
+          <t>402823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>157330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199289</t>
+          <t>201934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149627</t>
+          <t>151715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184449</t>
+          <t>184172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320082</t>
+          <t>318532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375182</t>
+          <t>373932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102696</t>
+          <t>99796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>29498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118170</t>
+          <t>116432</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68902</t>
+          <t>69533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>313070</t>
+          <t>310626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73139</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92556</t>
+          <t>93361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110486</t>
+          <t>118729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399099</t>
+          <t>399226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248931</t>
+          <t>251614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>563123</t>
+          <t>559957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>71110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307954</t>
+          <t>308428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672627</t>
+          <t>666651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106124</t>
+          <t>108650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160655</t>
+          <t>160714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58568</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147588</t>
+          <t>148585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166686</t>
+          <t>160444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283350</t>
+          <t>281828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>393924</t>
+          <t>395750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460885</t>
+          <t>465615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>154797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391549</t>
+          <t>390417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>499104</t>
+          <t>470432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>831099</t>
+          <t>831185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>374437</t>
+          <t>374646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>442317</t>
+          <t>440209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>417405</t>
+          <t>417643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>735600</t>
+          <t>735204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>818165</t>
+          <t>818710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1250454</t>
+          <t>1299241</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>67314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100994</t>
+          <t>100853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81191</t>
+          <t>77169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126664</t>
+          <t>128194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153201</t>
+          <t>153462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215080</t>
+          <t>217244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>192821</t>
+          <t>193590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>238257</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256258</t>
+          <t>249051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>392411</t>
+          <t>389363</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>462416</t>
+          <t>463728</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>617782</t>
+          <t>608826</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129939</t>
+          <t>130512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173996</t>
+          <t>173464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>316473</t>
+          <t>315525</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>482262</t>
+          <t>485157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>459895</t>
+          <t>461821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>653167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114121</t>
+          <t>113519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156985</t>
+          <t>156336</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>141119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>195347</t>
+          <t>193631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>76773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121707</t>
+          <t>122952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>365648</t>
+          <t>364103</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>417060</t>
+          <t>414611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>454703</t>
+          <t>459115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>523079</t>
+          <t>527281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47695</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96058</t>
+          <t>93136</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161794</t>
+          <t>160533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204163</t>
+          <t>203799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222739</t>
+          <t>224161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286987</t>
+          <t>287702</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>325490</t>
+          <t>320405</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>481630</t>
+          <t>480929</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>386587</t>
+          <t>377860</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>526217</t>
+          <t>524076</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>775867</t>
+          <t>770638</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>981301</t>
+          <t>984237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1034006</t>
+          <t>1051038</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1514375</t>
+          <t>1507053</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1201448</t>
+          <t>1194065</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1620150</t>
+          <t>1620648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2477239</t>
+          <t>2461458</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3082410</t>
+          <t>3078096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1236325</t>
+          <t>1238268</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1836835</t>
+          <t>1846025</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1326498</t>
+          <t>1324674</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1889605</t>
+          <t>1923417</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2612459</t>
+          <t>2607934</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3440556</t>
+          <t>3417644</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67220</t>
+          <t>73990</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>57775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86503</t>
+          <t>94778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>73799</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77330</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>130647</t>
+          <t>147789</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111123</t>
+          <t>124783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155361</t>
+          <t>171531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>236961</t>
+          <t>261784</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215254</t>
+          <t>236133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260155</t>
+          <t>285557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>216344</t>
+          <t>236269</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198959</t>
+          <t>216909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237004</t>
+          <t>255800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>453305</t>
+          <t>498054</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423976</t>
+          <t>468772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482336</t>
+          <t>527814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>187629</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166843</t>
+          <t>175270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>208673</t>
+          <t>223006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159847</t>
+          <t>170160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143243</t>
+          <t>151847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>177865</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>368626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>320674</t>
+          <t>341925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>377294</t>
+          <t>397755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>491810</t>
+          <t>534240</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>491810</t>
+          <t>534240</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491810</t>
+          <t>534240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>439618</t>
+          <t>480228</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439618</t>
+          <t>480228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>439618</t>
+          <t>480228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>931428</t>
+          <t>1014469</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>931428</t>
+          <t>1014469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>931428</t>
+          <t>1014469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53516</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>48275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>78400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>47961</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>59908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>95562</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79148</t>
+          <t>90243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113496</t>
+          <t>128727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206294</t>
+          <t>220148</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186297</t>
+          <t>197694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228371</t>
+          <t>240490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>169308</t>
+          <t>191024</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153454</t>
+          <t>173437</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186422</t>
+          <t>208610</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>375602</t>
+          <t>411172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>347872</t>
+          <t>383271</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>402823</t>
+          <t>442562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>178467</t>
+          <t>187658</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157330</t>
+          <t>166709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201934</t>
+          <t>210165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>167355</t>
+          <t>179128</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>161511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184172</t>
+          <t>197207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>345822</t>
+          <t>366786</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318532</t>
+          <t>335828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373932</t>
+          <t>394201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>438277</t>
+          <t>468429</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>438277</t>
+          <t>468429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438277</t>
+          <t>468429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>378709</t>
+          <t>418113</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378709</t>
+          <t>418113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378709</t>
+          <t>418113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>816986</t>
+          <t>886542</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816986</t>
+          <t>886542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>816986</t>
+          <t>886542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58957</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>53216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99796</t>
+          <t>84491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>86066</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116432</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>189394</t>
+          <t>213524</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69533</t>
+          <t>190348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310626</t>
+          <t>235580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82695</t>
+          <t>93721</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73120</t>
+          <t>82375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93361</t>
+          <t>105666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>272088</t>
+          <t>307245</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118729</t>
+          <t>285928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399226</t>
+          <t>331916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407331</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251614</t>
+          <t>156123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>559957</t>
+          <t>199992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60828</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71110</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>468160</t>
+          <t>245004</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308428</t>
+          <t>221881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666651</t>
+          <t>268071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>655682</t>
+          <t>457392</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>655682</t>
+          <t>457392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>655682</t>
+          <t>457392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160845</t>
+          <t>180922</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>160845</t>
+          <t>180922</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>160845</t>
+          <t>180922</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>816527</t>
+          <t>638314</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>816527</t>
+          <t>638314</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>816527</t>
+          <t>638314</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>129376</t>
+          <t>147878</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108650</t>
+          <t>125341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160714</t>
+          <t>171918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>110262</t>
+          <t>129964</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>112175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148585</t>
+          <t>150562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>239637</t>
+          <t>277842</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160444</t>
+          <t>249709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281828</t>
+          <t>311343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>429710</t>
+          <t>468008</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>395750</t>
+          <t>433991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465615</t>
+          <t>501084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>299308</t>
+          <t>336913</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154797</t>
+          <t>312056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390417</t>
+          <t>362874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>729018</t>
+          <t>804921</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470432</t>
+          <t>759509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>831185</t>
+          <t>842639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>409405</t>
+          <t>444778</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>374646</t>
+          <t>412294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>440209</t>
+          <t>480971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540024</t>
+          <t>364244</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>417643</t>
+          <t>339815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>735204</t>
+          <t>389873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>949430</t>
+          <t>809021</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>818710</t>
+          <t>765462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1299241</t>
+          <t>851574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>968491</t>
+          <t>1060664</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>968491</t>
+          <t>1060664</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>968491</t>
+          <t>1060664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>949594</t>
+          <t>831121</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>949594</t>
+          <t>831121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>949594</t>
+          <t>831121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1918086</t>
+          <t>1891785</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1918086</t>
+          <t>1891785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1918086</t>
+          <t>1891785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83468</t>
+          <t>122284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67314</t>
+          <t>102416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100853</t>
+          <t>142499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>106346</t>
+          <t>133171</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77169</t>
+          <t>117713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128194</t>
+          <t>151808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>189814</t>
+          <t>255455</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153462</t>
+          <t>228891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>217244</t>
+          <t>282944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>215354</t>
+          <t>242310</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>193590</t>
+          <t>219195</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>269190</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>335497</t>
+          <t>341627</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>249051</t>
+          <t>317580</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>389363</t>
+          <t>364218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>550852</t>
+          <t>583937</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>463728</t>
+          <t>550798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>621066</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>151810</t>
+          <t>166896</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130512</t>
+          <t>144913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173464</t>
+          <t>192468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>369853</t>
+          <t>322911</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315525</t>
+          <t>300685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>485157</t>
+          <t>348916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>521662</t>
+          <t>489807</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461821</t>
+          <t>456730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>653167</t>
+          <t>521909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>450632</t>
+          <t>531490</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>450632</t>
+          <t>531490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>450632</t>
+          <t>531490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>811696</t>
+          <t>797709</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>811696</t>
+          <t>797709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>811696</t>
+          <t>797709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1262328</t>
+          <t>1329199</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1262328</t>
+          <t>1329199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1262328</t>
+          <t>1329199</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>38969</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50714</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>133842</t>
+          <t>149088</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>113519</t>
+          <t>125926</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156336</t>
+          <t>171375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>166291</t>
+          <t>188058</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>141119</t>
+          <t>162956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>193631</t>
+          <t>217300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>98712</t>
+          <t>102416</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76773</t>
+          <t>79697</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122952</t>
+          <t>122310</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>392134</t>
+          <t>436406</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>364103</t>
+          <t>410725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>414611</t>
+          <t>464078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>490846</t>
+          <t>538822</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>459115</t>
+          <t>505057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>527281</t>
+          <t>573904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69795</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>81765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>182490</t>
+          <t>200745</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160533</t>
+          <t>175565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203799</t>
+          <t>223576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>252285</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224161</t>
+          <t>230588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287702</t>
+          <t>291109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>200956</t>
+          <t>200727</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>200956</t>
+          <t>200727</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>200956</t>
+          <t>200727</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>708466</t>
+          <t>786240</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>708466</t>
+          <t>786240</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>708466</t>
+          <t>786240</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>909422</t>
+          <t>986967</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>909422</t>
+          <t>986967</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>909422</t>
+          <t>986967</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>424985</t>
+          <t>509916</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>320405</t>
+          <t>461898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>480929</t>
+          <t>552544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>473244</t>
+          <t>553878</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>377860</t>
+          <t>517432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>524076</t>
+          <t>598553</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>898230</t>
+          <t>1063793</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>770638</t>
+          <t>1006129</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>984237</t>
+          <t>1126730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1376425</t>
+          <t>1508190</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1051038</t>
+          <t>1439694</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1507053</t>
+          <t>1563538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1495286</t>
+          <t>1635960</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1194065</t>
+          <t>1587218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1620648</t>
+          <t>1687195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2871711</t>
+          <t>3144150</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2461458</t>
+          <t>3066297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3078096</t>
+          <t>3232203</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1404438</t>
+          <t>1234836</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1238268</t>
+          <t>1183589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1846025</t>
+          <t>1305543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1480397</t>
+          <t>1304496</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1324674</t>
+          <t>1259533</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1923417</t>
+          <t>1359122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2884835</t>
+          <t>2539332</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2607934</t>
+          <t>2458905</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3417644</t>
+          <t>2619954</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3205848</t>
+          <t>3252942</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3205848</t>
+          <t>3252942</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3205848</t>
+          <t>3252942</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3448928</t>
+          <t>3494334</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3448928</t>
+          <t>3494334</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3448928</t>
+          <t>3494334</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6654776</t>
+          <t>6747276</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6654776</t>
+          <t>6747276</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6654776</t>
+          <t>6747276</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
